--- a/docs/bidding_samples/mau_mock_bidding.xlsx
+++ b/docs/bidding_samples/mau_mock_bidding.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q&amp;A'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Master Schedule'!$A$1:$F$35</definedName>
   </definedNames>
@@ -133,14 +133,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -712,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G2" s="3">
-        <f>SUM(G3,G4,G5,G6,G7,G8)</f>
+        <f>SUM(G3,G6,G9,G12,G15,G18)</f>
         <v/>
       </c>
     </row>
@@ -816,29 +816,15 @@
           <t>Kick-off và quản lý PoC</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: kick-off và quản lý poc</t>
-        </is>
+      <c r="G3" s="5">
+        <f>SUM(G4,G5)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -846,14 +832,14 @@
           <t>PoC</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Khảo sát dữ liệu &amp; yêu cầu</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Kick-off và quản lý PoC – phần 1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -862,18 +848,18 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: khảo sát dữ liệu &amp; yêu cầu</t>
+          <t>Kết quả: kick-off và quản lý poc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -881,14 +867,14 @@
           <t>PoC</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Chuẩn bị dữ liệu mẫu</t>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Kick-off và quản lý PoC – phần 2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -897,28 +883,18 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: chuẩn bị dữ liệu mẫu</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>data_prep</t>
+          <t>Kết quả: kick-off và quản lý poc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -928,37 +904,18 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Dựng prototype Chat API</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: dựng prototype chat api</t>
-        </is>
+          <t>Khảo sát dữ liệu &amp; yêu cầu</t>
+        </is>
+      </c>
+      <c r="G6" s="5">
+        <f>SUM(G7,G8)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -966,44 +923,34 @@
           <t>PoC</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Đánh giá kết quả PoC</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Khảo sát dữ liệu &amp; yêu cầu – phần 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: đánh giá kết quả poc</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>evaluation</t>
+          <t>Kết quả: khảo sát dữ liệu &amp; yêu cầu</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1011,437 +958,461 @@
           <t>PoC</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Test và nghiệm thu PoC</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Khảo sát dữ liệu &amp; yêu cầu – phần 2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1.3, 1.4, 1.5</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: test và nghiệm thu poc</t>
+          <t>Kết quả: khảo sát dữ liệu &amp; yêu cầu</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>PoC</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Total PoC</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="7">
-        <f>SUM(G2)</f>
-        <v/>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Chuẩn bị dữ liệu mẫu</t>
+        </is>
+      </c>
+      <c r="G9" s="5">
+        <f>SUM(G10,G11)</f>
+        <v/>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Giai đoạn MVP</t>
-        </is>
-      </c>
-      <c r="G10" s="3">
-        <f>SUM(G11,G14,G17,G20,G23,G24,G25,G26,G27)</f>
-        <v/>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Chuẩn bị dữ liệu mẫu – phần 1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: chuẩn bị dữ liệu mẫu</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>data_prep</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Quản lý dự án MVP</t>
-        </is>
-      </c>
-      <c r="G11" s="8">
-        <f>SUM(G12,G13)</f>
-        <v/>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1.6</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Chuẩn bị dữ liệu mẫu – phần 2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: chuẩn bị dữ liệu mẫu</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>data_prep</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Quản lý dự án MVP – phần 1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: quản lý dự án mvp</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Dựng prototype Chat API</t>
+        </is>
+      </c>
+      <c r="G12" s="5">
+        <f>SUM(G13,G14)</f>
+        <v/>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Quản lý dự án MVP – phần 2</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Dựng prototype Chat API – phần 1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: quản lý dự án mvp</t>
+          <t>Kết quả: dựng prototype chat api</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Phân tích &amp; thiết kế chi tiết</t>
-        </is>
-      </c>
-      <c r="G14" s="8">
-        <f>SUM(G15,G16)</f>
-        <v/>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Dựng prototype Chat API – phần 2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: dựng prototype chat api</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Phân tích &amp; thiết kế chi tiết – phần 1</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: phân tích &amp; thiết kế chi tiết</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Đánh giá kết quả PoC</t>
+        </is>
+      </c>
+      <c r="G15" s="5">
+        <f>SUM(G16,G17)</f>
+        <v/>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Phân tích &amp; thiết kế chi tiết – phần 2</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Đánh giá kết quả PoC – phần 1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: phân tích &amp; thiết kế chi tiết</t>
+          <t>Kết quả: đánh giá kết quả poc</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>evaluation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Chuẩn bị &amp; làm sạch dữ liệu</t>
-        </is>
-      </c>
-      <c r="G17" s="8">
-        <f>SUM(G18,G19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2.2</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Đánh giá kết quả PoC – phần 2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: đánh giá kết quả poc</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>evaluation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Chuẩn bị &amp; làm sạch dữ liệu – phần 1</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: chuẩn bị &amp; làm sạch dữ liệu</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>data_prep</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu PoC</t>
+        </is>
+      </c>
+      <c r="G18" s="5">
+        <f>SUM(G19,G20)</f>
+        <v/>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1.3, 1.4, 1.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Chuẩn bị &amp; làm sạch dữ liệu – phần 2</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu PoC – phần 1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: chuẩn bị &amp; làm sạch dữ liệu</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>data_prep</t>
+          <t>Kết quả: test và nghiệm thu poc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Xây dựng Chat API</t>
-        </is>
-      </c>
-      <c r="G20" s="8">
-        <f>SUM(G21,G22)</f>
-        <v/>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2.2</t>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu PoC – phần 2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: test và nghiệm thu poc</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2.4.1</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Xây dựng Chat API – phần 1</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: xây dựng chat api</t>
-        </is>
-      </c>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>PoC</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Total PoC</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="8">
+        <f>SUM(G2)</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1449,34 +1420,20 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Xây dựng Chat API – phần 2</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: xây dựng chat api</t>
-        </is>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Giai đoạn MVP</t>
+        </is>
+      </c>
+      <c r="G22" s="3">
+        <f>SUM(G23,G26,G29,G32,G35,G38,G41,G44,G47)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1486,42 +1443,23 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Xây dựng Web chat</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>4</v>
+          <t>Quản lý dự án MVP</t>
+        </is>
+      </c>
+      <c r="G23" s="5">
+        <f>SUM(G24,G25)</f>
+        <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: xây dựng web chat</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>integration</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1529,14 +1467,14 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Giao diện người dùng</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Quản lý dự án MVP – phần 1</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1545,23 +1483,18 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: giao diện người dùng</t>
+          <t>Kết quả: quản lý dự án mvp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1569,44 +1502,34 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Bộ đánh giá chất lượng</t>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Quản lý dự án MVP – phần 2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: bộ đánh giá chất lượng</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>evaluation</t>
+          <t>Kết quả: quản lý dự án mvp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1616,37 +1539,18 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Test và nghiệm thu MVP</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2.3, 2.4, 2.5, 2.6, 2.7</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: test và nghiệm thu mvp</t>
-        </is>
+          <t>Phân tích &amp; thiết kế chi tiết</t>
+        </is>
+      </c>
+      <c r="G26" s="5">
+        <f>SUM(G27,G28)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1654,9 +1558,9 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Tài liệu và bàn giao</t>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Phân tích &amp; thiết kế chi tiết – phần 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1670,82 +1574,94 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: tài liệu và bàn giao</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>documentation</t>
+          <t>Kết quả: phân tích &amp; thiết kế chi tiết</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Total MVP</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="7">
-        <f>SUM(G10)</f>
-        <v/>
-      </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Phân tích &amp; thiết kế chi tiết – phần 2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: phân tích &amp; thiết kế chi tiết</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="G29" s="3">
-        <f>SUM(G30,G31,G32,G33,G34,G35,G36,G37,G38,G39,G40,G41)</f>
-        <v/>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Chuẩn bị &amp; làm sạch dữ liệu</t>
+        </is>
+      </c>
+      <c r="G29" s="5">
+        <f>SUM(G30,G31)</f>
+        <v/>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Quản lý triển khai – đợt 1</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Chuẩn bị &amp; làm sạch dữ liệu – phần 1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1754,38 +1670,38 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: quản lý triển khai – đợt 1</t>
+          <t>Kết quả: chuẩn bị &amp; làm sạch dữ liệu</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>data_prep</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Quản lý triển khai – đợt 2</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Chuẩn bị &amp; làm sạch dữ liệu – phần 2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1794,203 +1710,160 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: quản lý triển khai – đợt 2</t>
+          <t>Kết quả: chuẩn bị &amp; làm sạch dữ liệu</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>data_prep</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Hardening &amp; bảo mật – đợt 1</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>7</v>
+          <t>Xây dựng Chat API</t>
+        </is>
+      </c>
+      <c r="G32" s="5">
+        <f>SUM(G33,G34)</f>
+        <v/>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: hardening &amp; bảo mật – đợt 1</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Hardening &amp; bảo mật – đợt 2</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Xây dựng Chat API – phần 1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: hardening &amp; bảo mật – đợt 2</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>security</t>
+          <t>Kết quả: xây dựng chat api</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Mở rộng Vector index – đợt 1</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Xây dựng Chat API – phần 2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: mở rộng vector index – đợt 1</t>
+          <t>Kết quả: xây dựng chat api</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Mở rộng Vector index – đợt 2</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>7</v>
+          <t>Xây dựng Web chat</t>
+        </is>
+      </c>
+      <c r="G35" s="5">
+        <f>SUM(G36,G37)</f>
+        <v/>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: mở rộng vector index – đợt 2</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Giám sát &amp; vận hành – đợt 1</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Xây dựng Web chat – phần 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1999,38 +1872,38 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: giám sát &amp; vận hành – đợt 1</t>
+          <t>Kết quả: xây dựng web chat</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>integration</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Giám sát &amp; vận hành – đợt 2</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Xây dựng Web chat – phần 2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2039,118 +1912,99 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: giám sát &amp; vận hành – đợt 2</t>
+          <t>Kết quả: xây dựng web chat</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>integration</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>UAT và nghiệm thu – đợt 1</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>6</v>
+          <t>Giao diện người dùng</t>
+        </is>
+      </c>
+      <c r="G38" s="5">
+        <f>SUM(G39,G40)</f>
+        <v/>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3.5, 3.6</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Kết quả: uat và nghiệm thu – đợt 1</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>UAT và nghiệm thu – đợt 2</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Giao diện người dùng – phần 1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>3.5, 3.6</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: uat và nghiệm thu – đợt 2</t>
+          <t>Kết quả: giao diện người dùng</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.6.2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Đào tạo &amp; bàn giao – đợt 1</t>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Giao diện người dùng – phần 2</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2159,95 +2013,882 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Kết quả: đào tạo &amp; bàn giao – đợt 1</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>documentation</t>
+          <t>Kết quả: giao diện người dùng</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Bộ đánh giá chất lượng</t>
+        </is>
+      </c>
+      <c r="G41" s="5">
+        <f>SUM(G42,G43)</f>
+        <v/>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2.7.1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Bộ đánh giá chất lượng – phần 1</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: bộ đánh giá chất lượng</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2.7.2</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Bộ đánh giá chất lượng – phần 2</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: bộ đánh giá chất lượng</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu MVP</t>
+        </is>
+      </c>
+      <c r="G44" s="5">
+        <f>SUM(G45,G46)</f>
+        <v/>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2.3, 2.4, 2.5, 2.6, 2.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2.8.1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu MVP – phần 1</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: test và nghiệm thu mvp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2.8.2</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Test và nghiệm thu MVP – phần 2</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: test và nghiệm thu mvp</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Tài liệu và bàn giao</t>
+        </is>
+      </c>
+      <c r="G47" s="5">
+        <f>SUM(G48,G49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Tài liệu và bàn giao – phần 1</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: tài liệu và bàn giao</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2.9.2</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Tài liệu và bàn giao – phần 2</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: tài liệu và bàn giao</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Total MVP</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="8">
+        <f>SUM(G22)</f>
+        <v/>
+      </c>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="G51" s="3">
+        <f>SUM(G52,G53,G54,G55,G56,G57,G58,G59,G60,G61,G62,G63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Quản lý triển khai – đợt 1</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: quản lý triển khai – đợt 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Quản lý triển khai – đợt 2</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: quản lý triển khai – đợt 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Hardening &amp; bảo mật – đợt 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: hardening &amp; bảo mật – đợt 1</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Hardening &amp; bảo mật – đợt 2</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: hardening &amp; bảo mật – đợt 2</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Mở rộng Vector index – đợt 1</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: mở rộng vector index – đợt 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Mở rộng Vector index – đợt 2</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: mở rộng vector index – đợt 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Giám sát &amp; vận hành – đợt 1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: giám sát &amp; vận hành – đợt 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Giám sát &amp; vận hành – đợt 2</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: giám sát &amp; vận hành – đợt 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>UAT và nghiệm thu – đợt 1</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>3.5, 3.6</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: uat và nghiệm thu – đợt 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>UAT và nghiệm thu – đợt 2</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>3.5, 3.6</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: uat và nghiệm thu – đợt 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Đào tạo &amp; bàn giao – đợt 1</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Kết quả: đào tạo &amp; bàn giao – đợt 1</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Đào tạo &amp; bàn giao – đợt 2</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Kết quả: đào tạo &amp; bàn giao – đợt 2</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Total Production</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="7">
-        <f>SUM(G29)</f>
-        <v/>
-      </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="8">
+        <f>SUM(G51)</f>
+        <v/>
+      </c>
+      <c r="H64" s="6" t="n"/>
+      <c r="I64" s="6" t="n"/>
+      <c r="J64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Grand total</t>
         </is>
       </c>
-      <c r="G43" s="3">
-        <f>SUM(G9,G28,G42)</f>
+      <c r="G65" s="3">
+        <f>SUM(G21,G50,G64)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2455,44 +3096,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <f>SUM(B2:B4)</f>
         <v/>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <f>SUM(C2:C4)</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <f>SUM(D2:D4)</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>SUM(E2:E4)</f>
         <v/>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <f>SUM(F2:F4)</f>
         <v/>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <f>SUM(G2:G4)</f>
         <v/>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <f>SUM(H2:H4)</f>
         <v/>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="8">
         <f>SUM(I2:I4)</f>
         <v/>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="8">
         <f>SUM(J2:J4)</f>
         <v/>
       </c>
@@ -2557,7 +3198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:AD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2578,6 +3219,18 @@
     <col width="6.5" customWidth="1" min="16" max="16"/>
     <col width="6.5" customWidth="1" min="17" max="17"/>
     <col width="6.5" customWidth="1" min="18" max="18"/>
+    <col width="6.5" customWidth="1" min="19" max="19"/>
+    <col width="6.5" customWidth="1" min="20" max="20"/>
+    <col width="6.5" customWidth="1" min="21" max="21"/>
+    <col width="6.5" customWidth="1" min="22" max="22"/>
+    <col width="6.5" customWidth="1" min="23" max="23"/>
+    <col width="6.5" customWidth="1" min="24" max="24"/>
+    <col width="6.5" customWidth="1" min="25" max="25"/>
+    <col width="6.5" customWidth="1" min="26" max="26"/>
+    <col width="6.5" customWidth="1" min="27" max="27"/>
+    <col width="6.5" customWidth="1" min="28" max="28"/>
+    <col width="6.5" customWidth="1" min="29" max="29"/>
+    <col width="6.5" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2613,62 +3266,122 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>19/10</t>
+          <t>26/10</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>26/10</t>
+          <t>02/11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>02/11</t>
+          <t>09/11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>09/11</t>
+          <t>16/11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>16/11</t>
+          <t>23/11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>23/11</t>
+          <t>30/11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>30/11</t>
+          <t>07/12</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>07/12</t>
+          <t>14/12</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>14/12</t>
+          <t>21/12</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>21/12</t>
+          <t>28/12</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>28/12</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>11/01</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>18/01</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>25/01</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>01/02</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>08/02</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>15/02</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>22/02</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>01/03</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>08/03</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>15/03</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>22/03</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>29/03</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>05/04</t>
         </is>
       </c>
     </row>
@@ -2685,26 +3398,38 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>46322</v>
+        <v>46359</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="G2" s="12" t="n"/>
       <c r="H2" s="12" t="n"/>
-      <c r="I2" s="13" t="n"/>
-      <c r="J2" s="13" t="n"/>
-      <c r="K2" s="13" t="n"/>
-      <c r="L2" s="13" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
       <c r="M2" s="13" t="n"/>
       <c r="N2" s="13" t="n"/>
       <c r="O2" s="13" t="n"/>
       <c r="P2" s="13" t="n"/>
       <c r="Q2" s="13" t="n"/>
       <c r="R2" s="13" t="n"/>
+      <c r="S2" s="13" t="n"/>
+      <c r="T2" s="13" t="n"/>
+      <c r="U2" s="13" t="n"/>
+      <c r="V2" s="13" t="n"/>
+      <c r="W2" s="13" t="n"/>
+      <c r="X2" s="13" t="n"/>
+      <c r="Y2" s="13" t="n"/>
+      <c r="Z2" s="13" t="n"/>
+      <c r="AA2" s="13" t="n"/>
+      <c r="AB2" s="13" t="n"/>
+      <c r="AC2" s="13" t="n"/>
+      <c r="AD2" s="13" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2723,16 +3448,16 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>46315</v>
+        <v>46331</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G3" s="16" t="n"/>
-      <c r="H3" s="13" t="n"/>
+      <c r="H3" s="16" t="n"/>
       <c r="I3" s="13" t="n"/>
       <c r="J3" s="13" t="n"/>
       <c r="K3" s="13" t="n"/>
@@ -2743,6 +3468,18 @@
       <c r="P3" s="13" t="n"/>
       <c r="Q3" s="13" t="n"/>
       <c r="R3" s="13" t="n"/>
+      <c r="S3" s="13" t="n"/>
+      <c r="T3" s="13" t="n"/>
+      <c r="U3" s="13" t="n"/>
+      <c r="V3" s="13" t="n"/>
+      <c r="W3" s="13" t="n"/>
+      <c r="X3" s="13" t="n"/>
+      <c r="Y3" s="13" t="n"/>
+      <c r="Z3" s="13" t="n"/>
+      <c r="AA3" s="13" t="n"/>
+      <c r="AB3" s="13" t="n"/>
+      <c r="AC3" s="13" t="n"/>
+      <c r="AD3" s="13" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2761,16 +3498,16 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>46315</v>
+        <v>46331</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G4" s="16" t="n"/>
-      <c r="H4" s="13" t="n"/>
+      <c r="H4" s="16" t="n"/>
       <c r="I4" s="13" t="n"/>
       <c r="J4" s="13" t="n"/>
       <c r="K4" s="13" t="n"/>
@@ -2781,6 +3518,18 @@
       <c r="P4" s="13" t="n"/>
       <c r="Q4" s="13" t="n"/>
       <c r="R4" s="13" t="n"/>
+      <c r="S4" s="13" t="n"/>
+      <c r="T4" s="13" t="n"/>
+      <c r="U4" s="13" t="n"/>
+      <c r="V4" s="13" t="n"/>
+      <c r="W4" s="13" t="n"/>
+      <c r="X4" s="13" t="n"/>
+      <c r="Y4" s="13" t="n"/>
+      <c r="Z4" s="13" t="n"/>
+      <c r="AA4" s="13" t="n"/>
+      <c r="AB4" s="13" t="n"/>
+      <c r="AC4" s="13" t="n"/>
+      <c r="AD4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2799,18 +3548,18 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>46316</v>
+        <v>46332</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>46317</v>
+        <v>46343</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
       <c r="K5" s="13" t="n"/>
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="13" t="n"/>
@@ -2819,6 +3568,18 @@
       <c r="P5" s="13" t="n"/>
       <c r="Q5" s="13" t="n"/>
       <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2837,17 +3598,17 @@
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>46316</v>
+        <v>46332</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="13" t="n"/>
       <c r="L6" s="13" t="n"/>
@@ -2857,6 +3618,18 @@
       <c r="P6" s="13" t="n"/>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="13" t="n"/>
+      <c r="Z6" s="13" t="n"/>
+      <c r="AA6" s="13" t="n"/>
+      <c r="AB6" s="13" t="n"/>
+      <c r="AC6" s="13" t="n"/>
+      <c r="AD6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2875,17 +3648,17 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>46316</v>
+        <v>46332</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
       <c r="J7" s="13" t="n"/>
       <c r="K7" s="13" t="n"/>
       <c r="L7" s="13" t="n"/>
@@ -2895,6 +3668,18 @@
       <c r="P7" s="13" t="n"/>
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="13" t="n"/>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="13" t="n"/>
+      <c r="Y7" s="13" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="13" t="n"/>
+      <c r="AC7" s="13" t="n"/>
+      <c r="AD7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2913,19 +3698,19 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>46318</v>
+        <v>46344</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>46321</v>
+        <v>46353</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
@@ -2933,6 +3718,18 @@
       <c r="P8" s="13" t="n"/>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="13" t="n"/>
+      <c r="AC8" s="13" t="n"/>
+      <c r="AD8" s="13" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
@@ -2951,10 +3748,10 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>0</v>
@@ -2975,6 +3772,18 @@
       <c r="P9" s="13" t="n"/>
       <c r="Q9" s="13" t="n"/>
       <c r="R9" s="13" t="n"/>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
+      <c r="Z9" s="13" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="13" t="n"/>
+      <c r="AC9" s="13" t="n"/>
+      <c r="AD9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -2993,30 +3802,42 @@
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>46322</v>
+        <v>46359</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>46322</v>
+        <v>46359</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n"/>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="n"/>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
       <c r="O10" s="13" t="n"/>
       <c r="P10" s="13" t="n"/>
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="13" t="n"/>
+      <c r="AD10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr"/>
@@ -3031,26 +3852,38 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46323</v>
+        <v>46360</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>46345</v>
+        <v>46441</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G11" s="13" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="13" t="n"/>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="13" t="n"/>
-      <c r="R11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
+      <c r="P11" s="20" t="n"/>
+      <c r="Q11" s="20" t="n"/>
+      <c r="R11" s="20" t="n"/>
+      <c r="S11" s="20" t="n"/>
+      <c r="T11" s="20" t="n"/>
+      <c r="U11" s="20" t="n"/>
+      <c r="V11" s="20" t="n"/>
+      <c r="W11" s="20" t="n"/>
+      <c r="X11" s="20" t="n"/>
+      <c r="Y11" s="13" t="n"/>
+      <c r="Z11" s="13" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="13" t="n"/>
+      <c r="AC11" s="13" t="n"/>
+      <c r="AD11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3069,26 +3902,38 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>46323</v>
+        <v>46360</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>46329</v>
+        <v>46384</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G12" s="13" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
       <c r="J12" s="13" t="n"/>
       <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
-      <c r="O12" s="13" t="n"/>
-      <c r="P12" s="13" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="21" t="n"/>
+      <c r="P12" s="21" t="n"/>
       <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="13" t="n"/>
+      <c r="X12" s="13" t="n"/>
+      <c r="Y12" s="13" t="n"/>
+      <c r="Z12" s="13" t="n"/>
+      <c r="AA12" s="13" t="n"/>
+      <c r="AB12" s="13" t="n"/>
+      <c r="AC12" s="13" t="n"/>
+      <c r="AD12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3107,26 +3952,38 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>46323</v>
+        <v>46360</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>46329</v>
+        <v>46384</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G13" s="13" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
       <c r="J13" s="13" t="n"/>
       <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="13" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="21" t="n"/>
+      <c r="P13" s="21" t="n"/>
       <c r="Q13" s="13" t="n"/>
       <c r="R13" s="13" t="n"/>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="13" t="n"/>
+      <c r="Y13" s="13" t="n"/>
+      <c r="Z13" s="13" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="13" t="n"/>
+      <c r="AC13" s="13" t="n"/>
+      <c r="AD13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3145,26 +4002,38 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>46330</v>
+        <v>46385</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>46336</v>
+        <v>46407</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
       <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="13" t="n"/>
+      <c r="P14" s="21" t="n"/>
+      <c r="Q14" s="21" t="n"/>
+      <c r="R14" s="21" t="n"/>
+      <c r="S14" s="21" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="13" t="n"/>
+      <c r="Y14" s="13" t="n"/>
+      <c r="Z14" s="13" t="n"/>
+      <c r="AA14" s="13" t="n"/>
+      <c r="AB14" s="13" t="n"/>
+      <c r="AC14" s="13" t="n"/>
+      <c r="AD14" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3183,26 +4052,38 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>46330</v>
+        <v>46385</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>46332</v>
+        <v>46395</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G15" s="13" t="n"/>
       <c r="H15" s="13" t="n"/>
-      <c r="I15" s="21" t="n"/>
+      <c r="I15" s="13" t="n"/>
       <c r="J15" s="13" t="n"/>
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="13" t="n"/>
       <c r="M15" s="13" t="n"/>
       <c r="N15" s="13" t="n"/>
       <c r="O15" s="13" t="n"/>
-      <c r="P15" s="13" t="n"/>
-      <c r="Q15" s="13" t="n"/>
+      <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
       <c r="R15" s="13" t="n"/>
+      <c r="S15" s="13" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="13" t="n"/>
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="13" t="n"/>
+      <c r="Y15" s="13" t="n"/>
+      <c r="Z15" s="13" t="n"/>
+      <c r="AA15" s="13" t="n"/>
+      <c r="AB15" s="13" t="n"/>
+      <c r="AC15" s="13" t="n"/>
+      <c r="AD15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3221,26 +4102,38 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>46330</v>
+        <v>46385</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>46335</v>
+        <v>46407</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G16" s="13" t="n"/>
       <c r="H16" s="13" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
       <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="13" t="n"/>
+      <c r="P16" s="21" t="n"/>
+      <c r="Q16" s="21" t="n"/>
+      <c r="R16" s="21" t="n"/>
+      <c r="S16" s="21" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="13" t="n"/>
+      <c r="Z16" s="13" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="13" t="n"/>
+      <c r="AC16" s="13" t="n"/>
+      <c r="AD16" s="13" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3259,26 +4152,38 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>46330</v>
+        <v>46385</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>46335</v>
+        <v>46407</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G17" s="13" t="n"/>
       <c r="H17" s="13" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="13" t="n"/>
       <c r="M17" s="13" t="n"/>
       <c r="N17" s="13" t="n"/>
       <c r="O17" s="13" t="n"/>
-      <c r="P17" s="13" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="13" t="n"/>
+      <c r="P17" s="21" t="n"/>
+      <c r="Q17" s="21" t="n"/>
+      <c r="R17" s="21" t="n"/>
+      <c r="S17" s="21" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="13" t="n"/>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="13" t="n"/>
+      <c r="Y17" s="13" t="n"/>
+      <c r="Z17" s="13" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="13" t="n"/>
+      <c r="AC17" s="13" t="n"/>
+      <c r="AD17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3297,26 +4202,38 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>46330</v>
+        <v>46385</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>46331</v>
+        <v>46394</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G18" s="13" t="n"/>
       <c r="H18" s="13" t="n"/>
-      <c r="I18" s="21" t="n"/>
+      <c r="I18" s="13" t="n"/>
       <c r="J18" s="13" t="n"/>
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
       <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
       <c r="R18" s="13" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="13" t="n"/>
+      <c r="Y18" s="13" t="n"/>
+      <c r="Z18" s="13" t="n"/>
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="13" t="n"/>
+      <c r="AC18" s="13" t="n"/>
+      <c r="AD18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3335,19 +4252,19 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>46337</v>
+        <v>46408</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>46342</v>
+        <v>46429</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G19" s="13" t="n"/>
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="13" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
       <c r="L19" s="13" t="n"/>
       <c r="M19" s="13" t="n"/>
       <c r="N19" s="13" t="n"/>
@@ -3355,6 +4272,18 @@
       <c r="P19" s="13" t="n"/>
       <c r="Q19" s="13" t="n"/>
       <c r="R19" s="13" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
+      <c r="U19" s="21" t="n"/>
+      <c r="V19" s="21" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="13" t="n"/>
+      <c r="Y19" s="13" t="n"/>
+      <c r="Z19" s="13" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="13" t="n"/>
+      <c r="AC19" s="13" t="n"/>
+      <c r="AD19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3373,26 +4302,38 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>46323</v>
+        <v>46360</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>46328</v>
+        <v>46381</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G20" s="13" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
       <c r="J20" s="13" t="n"/>
       <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="21" t="n"/>
       <c r="P20" s="13" t="n"/>
       <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="13" t="n"/>
+      <c r="Y20" s="13" t="n"/>
+      <c r="Z20" s="13" t="n"/>
+      <c r="AA20" s="13" t="n"/>
+      <c r="AB20" s="13" t="n"/>
+      <c r="AC20" s="13" t="n"/>
+      <c r="AD20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
@@ -3411,10 +4352,10 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>46345</v>
+        <v>46441</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>46345</v>
+        <v>46441</v>
       </c>
       <c r="F21" s="17" t="n">
         <v>0</v>
@@ -3423,11 +4364,7 @@
       <c r="H21" s="13" t="n"/>
       <c r="I21" s="13" t="n"/>
       <c r="J21" s="13" t="n"/>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
+      <c r="K21" s="13" t="n"/>
       <c r="L21" s="13" t="n"/>
       <c r="M21" s="13" t="n"/>
       <c r="N21" s="13" t="n"/>
@@ -3435,6 +4372,22 @@
       <c r="P21" s="13" t="n"/>
       <c r="Q21" s="13" t="n"/>
       <c r="R21" s="13" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="13" t="n"/>
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="19" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="Y21" s="13" t="n"/>
+      <c r="Z21" s="13" t="n"/>
+      <c r="AA21" s="13" t="n"/>
+      <c r="AB21" s="13" t="n"/>
+      <c r="AC21" s="13" t="n"/>
+      <c r="AD21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr"/>
@@ -3449,10 +4402,10 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>46346</v>
+        <v>46442</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>46392</v>
+        <v>46486</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>33</v>
@@ -3461,14 +4414,26 @@
       <c r="H22" s="13" t="n"/>
       <c r="I22" s="13" t="n"/>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="22" t="n"/>
-      <c r="M22" s="22" t="n"/>
-      <c r="N22" s="22" t="n"/>
-      <c r="O22" s="22" t="n"/>
-      <c r="P22" s="22" t="n"/>
-      <c r="Q22" s="22" t="n"/>
-      <c r="R22" s="22" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="22" t="n"/>
+      <c r="Y22" s="22" t="n"/>
+      <c r="Z22" s="22" t="n"/>
+      <c r="AA22" s="22" t="n"/>
+      <c r="AB22" s="22" t="n"/>
+      <c r="AC22" s="22" t="n"/>
+      <c r="AD22" s="22" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3487,10 +4452,10 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>46346</v>
+        <v>46442</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>46356</v>
+        <v>46450</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>7</v>
@@ -3499,14 +4464,26 @@
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="13" t="n"/>
-      <c r="K23" s="23" t="n"/>
-      <c r="L23" s="23" t="n"/>
-      <c r="M23" s="23" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="n"/>
       <c r="N23" s="13" t="n"/>
       <c r="O23" s="13" t="n"/>
       <c r="P23" s="13" t="n"/>
       <c r="Q23" s="13" t="n"/>
       <c r="R23" s="13" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="13" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="23" t="n"/>
+      <c r="Y23" s="23" t="n"/>
+      <c r="Z23" s="13" t="n"/>
+      <c r="AA23" s="13" t="n"/>
+      <c r="AB23" s="13" t="n"/>
+      <c r="AC23" s="13" t="n"/>
+      <c r="AD23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3525,10 +4502,10 @@
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>46346</v>
+        <v>46442</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>46356</v>
+        <v>46450</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>7</v>
@@ -3537,14 +4514,26 @@
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="23" t="n"/>
-      <c r="L24" s="23" t="n"/>
-      <c r="M24" s="23" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
       <c r="O24" s="13" t="n"/>
       <c r="P24" s="13" t="n"/>
       <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="23" t="n"/>
+      <c r="Y24" s="23" t="n"/>
+      <c r="Z24" s="13" t="n"/>
+      <c r="AA24" s="13" t="n"/>
+      <c r="AB24" s="13" t="n"/>
+      <c r="AC24" s="13" t="n"/>
+      <c r="AD24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3563,10 +4552,10 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>7</v>
@@ -3577,12 +4566,24 @@
       <c r="J25" s="13" t="n"/>
       <c r="K25" s="13" t="n"/>
       <c r="L25" s="13" t="n"/>
-      <c r="M25" s="23" t="n"/>
-      <c r="N25" s="23" t="n"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="n"/>
       <c r="O25" s="13" t="n"/>
       <c r="P25" s="13" t="n"/>
       <c r="Q25" s="13" t="n"/>
       <c r="R25" s="13" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="23" t="n"/>
+      <c r="Z25" s="23" t="n"/>
+      <c r="AA25" s="23" t="n"/>
+      <c r="AB25" s="13" t="n"/>
+      <c r="AC25" s="13" t="n"/>
+      <c r="AD25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3601,10 +4602,10 @@
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>7</v>
@@ -3615,12 +4616,24 @@
       <c r="J26" s="13" t="n"/>
       <c r="K26" s="13" t="n"/>
       <c r="L26" s="13" t="n"/>
-      <c r="M26" s="23" t="n"/>
-      <c r="N26" s="23" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
       <c r="O26" s="13" t="n"/>
       <c r="P26" s="13" t="n"/>
       <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="23" t="n"/>
+      <c r="Z26" s="23" t="n"/>
+      <c r="AA26" s="23" t="n"/>
+      <c r="AB26" s="13" t="n"/>
+      <c r="AC26" s="13" t="n"/>
+      <c r="AD26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3639,10 +4652,10 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>7</v>
@@ -3653,12 +4666,24 @@
       <c r="J27" s="13" t="n"/>
       <c r="K27" s="13" t="n"/>
       <c r="L27" s="13" t="n"/>
-      <c r="M27" s="23" t="n"/>
-      <c r="N27" s="23" t="n"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="n"/>
       <c r="O27" s="13" t="n"/>
       <c r="P27" s="13" t="n"/>
       <c r="Q27" s="13" t="n"/>
       <c r="R27" s="13" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="13" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="13" t="n"/>
+      <c r="Y27" s="23" t="n"/>
+      <c r="Z27" s="23" t="n"/>
+      <c r="AA27" s="23" t="n"/>
+      <c r="AB27" s="13" t="n"/>
+      <c r="AC27" s="13" t="n"/>
+      <c r="AD27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3677,10 +4702,10 @@
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>7</v>
@@ -3691,12 +4716,24 @@
       <c r="J28" s="13" t="n"/>
       <c r="K28" s="13" t="n"/>
       <c r="L28" s="13" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="23" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="23" t="n"/>
+      <c r="Z28" s="23" t="n"/>
+      <c r="AA28" s="23" t="n"/>
+      <c r="AB28" s="13" t="n"/>
+      <c r="AC28" s="13" t="n"/>
+      <c r="AD28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3715,10 +4752,10 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>7</v>
@@ -3729,12 +4766,24 @@
       <c r="J29" s="13" t="n"/>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="13" t="n"/>
-      <c r="M29" s="23" t="n"/>
-      <c r="N29" s="23" t="n"/>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="n"/>
       <c r="O29" s="13" t="n"/>
       <c r="P29" s="13" t="n"/>
       <c r="Q29" s="13" t="n"/>
       <c r="R29" s="13" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="13" t="n"/>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="13" t="n"/>
+      <c r="Y29" s="23" t="n"/>
+      <c r="Z29" s="23" t="n"/>
+      <c r="AA29" s="23" t="n"/>
+      <c r="AB29" s="13" t="n"/>
+      <c r="AC29" s="13" t="n"/>
+      <c r="AD29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3753,10 +4802,10 @@
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>46357</v>
+        <v>46451</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>46365</v>
+        <v>46461</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>7</v>
@@ -3767,12 +4816,24 @@
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="13" t="n"/>
       <c r="L30" s="13" t="n"/>
-      <c r="M30" s="23" t="n"/>
-      <c r="N30" s="23" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
       <c r="P30" s="13" t="n"/>
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="23" t="n"/>
+      <c r="Z30" s="23" t="n"/>
+      <c r="AA30" s="23" t="n"/>
+      <c r="AB30" s="13" t="n"/>
+      <c r="AC30" s="13" t="n"/>
+      <c r="AD30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3791,10 +4852,10 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>46366</v>
+        <v>46462</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>46373</v>
+        <v>46469</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>6</v>
@@ -3806,11 +4867,23 @@
       <c r="K31" s="13" t="n"/>
       <c r="L31" s="13" t="n"/>
       <c r="M31" s="13" t="n"/>
-      <c r="N31" s="23" t="n"/>
-      <c r="O31" s="23" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
       <c r="P31" s="13" t="n"/>
       <c r="Q31" s="13" t="n"/>
       <c r="R31" s="13" t="n"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="13" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="13" t="n"/>
+      <c r="Y31" s="13" t="n"/>
+      <c r="Z31" s="13" t="n"/>
+      <c r="AA31" s="23" t="n"/>
+      <c r="AB31" s="23" t="n"/>
+      <c r="AC31" s="13" t="n"/>
+      <c r="AD31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3829,10 +4902,10 @@
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>46366</v>
+        <v>46462</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>46373</v>
+        <v>46469</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>6</v>
@@ -3844,11 +4917,23 @@
       <c r="K32" s="13" t="n"/>
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
-      <c r="N32" s="23" t="n"/>
-      <c r="O32" s="23" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
       <c r="P32" s="13" t="n"/>
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="13" t="n"/>
+      <c r="Z32" s="13" t="n"/>
+      <c r="AA32" s="23" t="n"/>
+      <c r="AB32" s="23" t="n"/>
+      <c r="AC32" s="13" t="n"/>
+      <c r="AD32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3867,10 +4952,10 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>46346</v>
+        <v>46442</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>46353</v>
+        <v>46449</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>6</v>
@@ -3879,14 +4964,26 @@
       <c r="H33" s="13" t="n"/>
       <c r="I33" s="13" t="n"/>
       <c r="J33" s="13" t="n"/>
-      <c r="K33" s="23" t="n"/>
-      <c r="L33" s="23" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
       <c r="M33" s="13" t="n"/>
       <c r="N33" s="13" t="n"/>
       <c r="O33" s="13" t="n"/>
       <c r="P33" s="13" t="n"/>
       <c r="Q33" s="13" t="n"/>
       <c r="R33" s="13" t="n"/>
+      <c r="S33" s="13" t="n"/>
+      <c r="T33" s="13" t="n"/>
+      <c r="U33" s="13" t="n"/>
+      <c r="V33" s="13" t="n"/>
+      <c r="W33" s="13" t="n"/>
+      <c r="X33" s="23" t="n"/>
+      <c r="Y33" s="23" t="n"/>
+      <c r="Z33" s="13" t="n"/>
+      <c r="AA33" s="13" t="n"/>
+      <c r="AB33" s="13" t="n"/>
+      <c r="AC33" s="13" t="n"/>
+      <c r="AD33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3905,10 +5002,10 @@
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>46346</v>
+        <v>46442</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>46353</v>
+        <v>46449</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>6</v>
@@ -3917,14 +5014,26 @@
       <c r="H34" s="13" t="n"/>
       <c r="I34" s="13" t="n"/>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="23" t="n"/>
-      <c r="L34" s="23" t="n"/>
+      <c r="K34" s="13" t="n"/>
+      <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
       <c r="P34" s="13" t="n"/>
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="13" t="n"/>
+      <c r="U34" s="13" t="n"/>
+      <c r="V34" s="13" t="n"/>
+      <c r="W34" s="13" t="n"/>
+      <c r="X34" s="23" t="n"/>
+      <c r="Y34" s="23" t="n"/>
+      <c r="Z34" s="13" t="n"/>
+      <c r="AA34" s="13" t="n"/>
+      <c r="AB34" s="13" t="n"/>
+      <c r="AC34" s="13" t="n"/>
+      <c r="AD34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -3943,10 +5052,10 @@
         </is>
       </c>
       <c r="D35" s="18" t="n">
-        <v>46392</v>
+        <v>46486</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>46392</v>
+        <v>46486</v>
       </c>
       <c r="F35" s="17" t="n">
         <v>0</v>
@@ -3962,7 +5071,19 @@
       <c r="O35" s="13" t="n"/>
       <c r="P35" s="13" t="n"/>
       <c r="Q35" s="13" t="n"/>
-      <c r="R35" s="19" t="inlineStr">
+      <c r="R35" s="13" t="n"/>
+      <c r="S35" s="13" t="n"/>
+      <c r="T35" s="13" t="n"/>
+      <c r="U35" s="13" t="n"/>
+      <c r="V35" s="13" t="n"/>
+      <c r="W35" s="13" t="n"/>
+      <c r="X35" s="13" t="n"/>
+      <c r="Y35" s="13" t="n"/>
+      <c r="Z35" s="13" t="n"/>
+      <c r="AA35" s="13" t="n"/>
+      <c r="AB35" s="13" t="n"/>
+      <c r="AC35" s="13" t="n"/>
+      <c r="AD35" s="19" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
